--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -18212,7 +18212,7 @@
       </c>
       <c r="J40" s="42" t="inlineStr">
         <is>
-          <t>Ik dacht dat ge STENEN-SPEL aan 't spelen waart met uw NONKEL!"</t>
+          <t>Ik dacht dat je STENEN-SPEL aan 't spelen was met je NONKEL!"</t>
         </is>
       </c>
       <c r="K40" s="33" t="inlineStr">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="J43" s="43" t="inlineStr">
         <is>
-          <t>Uw Oom Stoere is een Ezel, niet een slechte, zielloze, kind-dodende Machine.</t>
+          <t>Je Oom Stoere is een Ezel, niet een slechte, zielloze, kind-dodende Machine.</t>
         </is>
       </c>
       <c r="K43" s="33" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="J48" s="43" t="inlineStr">
         <is>
-          <t>"En waarom blijft ge dat ding Piet noemen?!"</t>
+          <t>"En waarom blijf je dat ding Piet noemen?!"</t>
         </is>
       </c>
       <c r="K48" s="33" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="J55" s="43" t="inlineStr">
         <is>
-          <t>Omdat ge een EZEL ZIJT!</t>
+          <t>Omdat je een EZEL BENT!</t>
         </is>
       </c>
       <c r="K55" s="33" t="inlineStr">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="J86" s="43" t="inlineStr">
         <is>
-          <t>Hebt ge {$NewName} ooit over ons verteld?</t>
+          <t>Heb je {$NewName} ooit over ons verteld?</t>
         </is>
       </c>
       <c r="K86" s="33" t="inlineStr">
@@ -34622,7 +34622,7 @@
       </c>
       <c r="J26" s="31" t="inlineStr">
         <is>
-          <t>Hoe kon ge dit aan uw Moeder aandoen?</t>
+          <t>Hoe kon je dit aan je Moeder aandoen?</t>
         </is>
       </c>
       <c r="K26" s="64" t="inlineStr">
@@ -34680,7 +34680,7 @@
       </c>
       <c r="J27" s="31" t="inlineStr">
         <is>
-          <t>Ik zag u zo graag...</t>
+          <t>Ik zag je zo graag...</t>
         </is>
       </c>
       <c r="K27" s="64" t="inlineStr">
@@ -34738,7 +34738,7 @@
       </c>
       <c r="J28" s="31" t="inlineStr">
         <is>
-          <t>Hoe kon ge zo onze soort opgeven?</t>
+          <t>Hoe kon je zo onze soort opgeven?</t>
         </is>
       </c>
       <c r="K28" s="64" t="inlineStr">
@@ -49169,7 +49169,7 @@
       </c>
       <c r="J52" s="43" t="inlineStr">
         <is>
-          <t>Ge kunt toch niet een Machine Profeet laten worden!</t>
+          <t>Je kunt toch niet een Machine Profeet laten worden!</t>
         </is>
       </c>
       <c r="K52" s="64" t="inlineStr">
@@ -52321,7 +52321,7 @@
       </c>
       <c r="J106" s="43" t="inlineStr">
         <is>
-          <t>Dus uw tantes en nonkels zijn met de Traktor Machine vertrokken om hen te gaan zoeken.</t>
+          <t>Dus je tantes en nonkels zijn met de Traktor Machine vertrokken om hen te gaan zoeken.</t>
         </is>
       </c>
       <c r="K106" s="64" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -47965,7 +47965,7 @@
       </c>
       <c r="J32" s="43" t="inlineStr">
         <is>
-          <t>Een Profeet rijdt op onze rug en bekeert vijanden tot bondgenoten, overal waar wij gaan.</t>
+          <t>Een Profeet rijdt op onze rug en bekeert vijanden tot bondgenoten, waar we ook gaan.</t>
         </is>
       </c>
       <c r="K32" s="64" t="inlineStr">
@@ -48027,7 +48027,7 @@
       </c>
       <c r="J33" s="43" t="inlineStr">
         <is>
-          <t>Een Profeet rijdt op onze rug en bekeert vijanden tot bondgenoten, overal waar wij gaan.</t>
+          <t>Zij rijden op onze rug en bekeren vijanden tot bondgenoten, waar we ook gaan.</t>
         </is>
       </c>
       <c r="K33" s="64" t="inlineStr">
@@ -51099,7 +51099,7 @@
       </c>
       <c r="J85" s="43" t="inlineStr">
         <is>
-          <t>Gij bent het levende bewijs dat Mensen het vermogen hebben om te veranderen.</t>
+          <t>Gij bent het levende bewijs dat Mensen boven zichzelf kunnen stijgen.</t>
         </is>
       </c>
       <c r="K85" s="64" t="inlineStr">
@@ -52321,7 +52321,7 @@
       </c>
       <c r="J106" s="43" t="inlineStr">
         <is>
-          <t>Dus je tantes en nonkels zijn met de Traktor Machine vertrokken om hen te gaan zoeken.</t>
+          <t>Dus je tantes en nonkels zijn met de Tractor-Machine vertrokken om hen te gaan zoeken.</t>
         </is>
       </c>
       <c r="K106" s="64" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -16522,7 +16522,7 @@
       </c>
       <c r="J11" s="42" t="inlineStr">
         <is>
-          <t>'t Gaat allemaal om wa da ge vanbinnen hebt en wa da ge wilt bereiken in deze wereld.</t>
+          <t>'t Gaat allemaal om wa dat ge vanbinnen hebt en wa dat ge wilt bereiken in deze wereld.</t>
         </is>
       </c>
       <c r="K11" s="33" t="inlineStr">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="J15" s="43" t="inlineStr">
         <is>
-          <t>Nie plezant.</t>
+          <t>Niet plezant.</t>
         </is>
       </c>
       <c r="K15" s="33" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="J20" s="43" t="inlineStr">
         <is>
-          <t>Geen zorgen, 'k kom terug om je te bezoeken.</t>
+          <t>Geen zorgen, 'k kom terug om u te bezoeken.</t>
         </is>
       </c>
       <c r="K20" s="33" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="J24" s="43" t="inlineStr">
         <is>
-          <t>Kleine, de wereld daarbuiten is nie veilig voor ezels. Da weet ge toch.</t>
+          <t>Kleine, de wereld daarbuiten is niet veilig voor ezels. Dat weet ge toch.</t>
         </is>
       </c>
       <c r="K24" s="33" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="J32" s="42" t="inlineStr">
         <is>
-          <t>'k Veronderstel da ge 't prototype misschien zou kunnen gebruiken...</t>
+          <t>'k Veronderstel dat ge 't prototype misschien zou kunnen gebruiken...</t>
         </is>
       </c>
       <c r="K32" s="33" t="inlineStr">
@@ -50113,7 +50113,7 @@
       </c>
       <c r="J68" s="42" t="inlineStr">
         <is>
-          <t>'k Geloof nie in leiders.</t>
+          <t>'k Geloof niet in leiders.</t>
         </is>
       </c>
       <c r="K68" s="64" t="inlineStr">
@@ -50345,7 +50345,7 @@
       </c>
       <c r="J72" s="43" t="inlineStr">
         <is>
-          <t>Kan mij nie schelen.</t>
+          <t>Kan mij niet schelen.</t>
         </is>
       </c>
       <c r="K72" s="64" t="inlineStr">
@@ -51273,7 +51273,7 @@
       </c>
       <c r="J88" s="43" t="inlineStr">
         <is>
-          <t>En op geen enkel moment gaat da proces mij weer in nen Ezel veranderen, hé?</t>
+          <t>En op geen enkel moment gaat dat proces mij weer in nen Ezel veranderen, hé?</t>
         </is>
       </c>
       <c r="K88" s="64" t="inlineStr">
@@ -52027,7 +52027,7 @@
       </c>
       <c r="J101" s="43" t="inlineStr">
         <is>
-          <t>Laat uw Moeder nie in de steek.</t>
+          <t>Laat uw Moeder niet in de steek.</t>
         </is>
       </c>
       <c r="K101" s="64" t="inlineStr">
@@ -52089,7 +52089,7 @@
       </c>
       <c r="J102" s="43" t="inlineStr">
         <is>
-          <t>Ze zal 't nie zeggen, maar ze heeft u nodig.</t>
+          <t>Ze zal 't niet zeggen, maar ze heeft u nodig.</t>
         </is>
       </c>
       <c r="K102" s="64" t="inlineStr">
@@ -53903,7 +53903,7 @@
       </c>
       <c r="J133" s="43" t="inlineStr">
         <is>
-          <t>Kleine, wilt ge echt een Profeet zijn voor da stelleke klootzakken?</t>
+          <t>Kleine, wilt ge echt een Profeet zijn voor dat stelleke klootzakken?</t>
         </is>
       </c>
       <c r="K133" s="64" t="inlineStr">
@@ -54839,7 +54839,7 @@
       </c>
       <c r="J149" s="43" t="inlineStr">
         <is>
-          <t>Verman je.</t>
+          <t>Verman u.</t>
         </is>
       </c>
       <c r="K149" s="64" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -50983,7 +50983,7 @@
       </c>
       <c r="J83" s="43" t="inlineStr">
         <is>
-          <t>Ge weet in uw Ziel dat een filosofische transformatie nu meer dan ooit noodzakelijk is.</t>
+          <t>Gij weet in uw Ziel dat een filosofische transformatie nu meer dan ooit noodzakelijk is.</t>
         </is>
       </c>
       <c r="K83" s="64" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -18212,7 +18212,7 @@
       </c>
       <c r="J40" s="42" t="inlineStr">
         <is>
-          <t>Ik dacht dat je STENEN-SPEL aan 't spelen was met je NONKEL!"</t>
+          <t>Ik dacht dat je STENEN-SPEL aan 't spelen was met je NONKEL!</t>
         </is>
       </c>
       <c r="K40" s="33" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="J41" s="43" t="inlineStr">
         <is>
-          <t>"Geen zorgen Kameraad Moeder, dit IS Nonkel Stoere—Piet."</t>
+          <t>Geen zorgen Kameraad Moeder, dit IS Nonkel Stoere—Piet.</t>
         </is>
       </c>
       <c r="K41" s="33" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="J48" s="43" t="inlineStr">
         <is>
-          <t>"En waarom blijf je dat ding Piet noemen?!"</t>
+          <t>En waarom blijf je dat ding Piet noemen?!</t>
         </is>
       </c>
       <c r="K48" s="33" t="inlineStr">
@@ -46367,7 +46367,7 @@
       </c>
       <c r="J5" s="43" t="inlineStr">
         <is>
-          <t>"*KUCH*"</t>
+          <t>*KUCH*</t>
         </is>
       </c>
       <c r="K5" s="64" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -20324,7 +20324,7 @@
       </c>
       <c r="J76" s="45" t="inlineStr">
         <is>
-          <t>Toen Luie stierf, probeerde ze de Hemelvaarts-zang-der-Ezel-zielen voor zichzelf te zingen.</t>
+          <t>Toen Luie stierf, probeerde ze het Hemelvaarts-zang-der-Ezel-zielen voor zichzelf te zingen.</t>
         </is>
       </c>
       <c r="K76" s="34" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -17888,7 +17888,7 @@
       </c>
       <c r="J34" s="44" t="inlineStr">
         <is>
-          <t>'k Start de initializer op. Geef mij een minuutje.</t>
+          <t>'k Start de initializer op. Geeft mij een minuutje.</t>
         </is>
       </c>
       <c r="K34" s="34" t="inlineStr">
@@ -19570,7 +19570,7 @@
       </c>
       <c r="J63" s="45" t="inlineStr">
         <is>
-          <t>Stevige. Stop.</t>
+          <t>Stevige. Stopt.</t>
         </is>
       </c>
       <c r="K63" s="34" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="J64" s="45" t="inlineStr">
         <is>
-          <t>Probeer de machine niet kapot te maken.</t>
+          <t>Probeert de Machine niet kapot te maken.</t>
         </is>
       </c>
       <c r="K64" s="34" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="J81" s="45" t="inlineStr">
         <is>
-          <t>Luister Stevige.</t>
+          <t>Luistert Stevige.</t>
         </is>
       </c>
       <c r="K81" s="34" t="inlineStr">
@@ -54044,7 +54044,7 @@
       </c>
       <c r="J135" s="45" t="inlineStr">
         <is>
-          <t>Ga dan.</t>
+          <t>Gaat dan.</t>
         </is>
       </c>
       <c r="K135" s="67" t="inlineStr">

--- a/excels/9_asses.masses_E9Proxy.xlsx
+++ b/excels/9_asses.masses_E9Proxy.xlsx
@@ -258,13 +258,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="0000B050"/>
+      </left>
+      <right style="thin">
+        <color rgb="0000B050"/>
+      </right>
+      <top style="thin">
+        <color rgb="0000B050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0000B050"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -567,6 +581,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16196,7 +16219,7 @@
           <t>Sonunda Teknopol Büyükşehir'e gidebilirim!</t>
         </is>
       </c>
-      <c r="J5" s="44" t="inlineStr">
+      <c r="J5" s="106" t="inlineStr">
         <is>
           <t>'k Kan eindelijk naar Technopolis!</t>
         </is>
@@ -16428,7 +16451,7 @@
           <t>Kuyu Bozuk Dayı... Eşek olmak o kadar korkunç bir şey mi?</t>
         </is>
       </c>
-      <c r="J9" s="45" t="inlineStr">
+      <c r="J9" s="107" t="inlineStr">
         <is>
           <t>Nonkel Stoere—Piet... is het zo erg om een Ezel te zijn?</t>
         </is>
@@ -16718,7 +16741,7 @@
           <t>O zaman, eşeklere karşı tarihsel önyargı göz önüne alındığında, eşek olmak...</t>
         </is>
       </c>
-      <c r="J14" s="45" t="inlineStr">
+      <c r="J14" s="107" t="inlineStr">
         <is>
           <t>Dan, gezien 't historisch vooroordeel tegen Ezels, is Ezel zijn...</t>
         </is>
@@ -16950,7 +16973,7 @@
           <t>Teknopol Büyükşehir'e mi gidiyorsun şimdi?</t>
         </is>
       </c>
-      <c r="J18" s="45" t="inlineStr">
+      <c r="J18" s="107" t="inlineStr">
         <is>
           <t>Ga je nu naar Technopolis...?</t>
         </is>
@@ -17248,7 +17271,7 @@
           <t>Ben de Teknopol Büyükşehir'i görmek istiyorum! Birlikte gidebiliriz!</t>
         </is>
       </c>
-      <c r="J23" s="45" t="inlineStr">
+      <c r="J23" s="107" t="inlineStr">
         <is>
           <t>Maar ik wil Technopolis ook zien! We kunnen samen gaan!</t>
         </is>
@@ -17306,7 +17329,7 @@
           <t>Evlat, dışarıdaki dünya eşekler için güvenli değil. Bunu biliyorsun.</t>
         </is>
       </c>
-      <c r="J24" s="49" t="inlineStr">
+      <c r="J24" s="108" t="inlineStr">
         <is>
           <t>Kleine, de wereld daarbuiten is niet veilig voor Ezels. Dat weet ge toch.</t>
         </is>
@@ -17886,7 +17909,7 @@
           <t xml:space="preserve">Bana bir dakika ver. Başlatıcıyı çalıştırayım. </t>
         </is>
       </c>
-      <c r="J34" s="44" t="inlineStr">
+      <c r="J34" s="106" t="inlineStr">
         <is>
           <t>'k Start de initializer op. Geeft mij een minuutje.</t>
         </is>
@@ -18234,9 +18257,9 @@
           <t>Ben de DAYI'nla senin TAŞLARLA oynadığınızı sanıyordum!</t>
         </is>
       </c>
-      <c r="J40" s="49" t="inlineStr">
-        <is>
-          <t>Ik dacht dat je STENEN-SPEL aan 't spelen was met je NONKEL!</t>
+      <c r="J40" s="108" t="inlineStr">
+        <is>
+          <t>Ik dacht dat je KEIEN-SPEL aan 't spelen was met je NONKEL!</t>
         </is>
       </c>
       <c r="K40" s="34" t="inlineStr">
@@ -18292,7 +18315,7 @@
           <t xml:space="preserve">Sakin ol Yoldaş Ana, bu Kuyu Bozuk Dayı. </t>
         </is>
       </c>
-      <c r="J41" s="49" t="inlineStr">
+      <c r="J41" s="108" t="inlineStr">
         <is>
           <t>Geen zorgen Kameraad Moeder, dit IS Nonkel Stoere—Piet.</t>
         </is>
@@ -18698,7 +18721,7 @@
           <t>Hem sen neden buna Kuyu diyip duruyorsun?</t>
         </is>
       </c>
-      <c r="J48" s="49" t="inlineStr">
+      <c r="J48" s="108" t="inlineStr">
         <is>
           <t>En waarom blijf je dat ding Piet noemen?!</t>
         </is>
@@ -19568,7 +19591,7 @@
           <t>Ana Eşek. Dur.</t>
         </is>
       </c>
-      <c r="J63" s="45" t="inlineStr">
+      <c r="J63" s="107" t="inlineStr">
         <is>
           <t>Stevige. Stopt.</t>
         </is>
@@ -19626,7 +19649,7 @@
           <t xml:space="preserve">Makine'yi kırmaya çalışma. </t>
         </is>
       </c>
-      <c r="J64" s="45" t="inlineStr">
+      <c r="J64" s="107" t="inlineStr">
         <is>
           <t>Probeert de Machine niet kapot te maken.</t>
         </is>
@@ -20322,7 +20345,7 @@
           <t xml:space="preserve">Tembel ölürken, kendisi için Eşek İlahisi'ni söylemeye çalıştı. </t>
         </is>
       </c>
-      <c r="J76" s="45" t="inlineStr">
+      <c r="J76" s="107" t="inlineStr">
         <is>
           <t>Toen Luie stierf, probeerde ze de Ezelenhemelvaartszangderzielen voor zichzelf te zingen.</t>
         </is>
@@ -20612,7 +20635,7 @@
           <t xml:space="preserve">Bak, Ana Eşek. </t>
         </is>
       </c>
-      <c r="J81" s="45" t="inlineStr">
+      <c r="J81" s="107" t="inlineStr">
         <is>
           <t>Luistert Stevige.</t>
         </is>
@@ -46390,7 +46413,7 @@
           <t>*ÖHÖ*</t>
         </is>
       </c>
-      <c r="J5" s="49" t="inlineStr">
+      <c r="J5" s="108" t="inlineStr">
         <is>
           <t>*KUCH*</t>
         </is>
@@ -46680,7 +46703,7 @@
           <t>Siz sikikler beni bir eşeğe çevirdiniz!</t>
         </is>
       </c>
-      <c r="J10" s="45" t="inlineStr">
+      <c r="J10" s="107" t="inlineStr">
         <is>
           <t>Gelle klootzakken hebt mij in nen Ezel veranderd!</t>
         </is>
@@ -47202,7 +47225,7 @@
           <t xml:space="preserve">Eskiden Hasta Eşek olarak tanınan Kul aracılığıyla sizlere Eşek Cenneti'nden sesleniyoruz. </t>
         </is>
       </c>
-      <c r="J19" s="45" t="inlineStr">
+      <c r="J19" s="107" t="inlineStr">
         <is>
           <t>Wij spreken tot U vanuit het Astrale Hiernamaals, door de Vazal voordien bekend als Snot Ezel.</t>
         </is>
@@ -47988,7 +48011,7 @@
           <t>Bir Peygamber sırtımıza oturur ve gittiğimiz her yerde düşmanları müttefiklere dönüştürür.</t>
         </is>
       </c>
-      <c r="J32" s="49" t="inlineStr">
+      <c r="J32" s="108" t="inlineStr">
         <is>
           <t>Een Profeet rijdt op onze rug en bekeert vijanden tot bondgenoten, waar we ook gaan.</t>
         </is>
@@ -48050,7 +48073,7 @@
           <t>Onlar sırtımıza oturur ve gittiğimiz her yerde düşmanları müttefiklere dönüştürürler.</t>
         </is>
       </c>
-      <c r="J33" s="49" t="inlineStr">
+      <c r="J33" s="108" t="inlineStr">
         <is>
           <t>Zij rijden op onze rug en bekeren vijanden tot bondgenoten, waar we ook gaan.</t>
         </is>
@@ -48894,7 +48917,7 @@
           <t xml:space="preserve">Siz iki Makine'den biri yeni Peygamber olacak. </t>
         </is>
       </c>
-      <c r="J47" s="45" t="inlineStr">
+      <c r="J47" s="107" t="inlineStr">
         <is>
           <t>Eén van U beide Machines zal onze Profeet worden.</t>
         </is>
@@ -51006,7 +51029,7 @@
           <t>Ruh'unun, felsefi bir dönüşüme şu an her zamankinden daha fazla ihtiyacı olduğunu biliyorsun.</t>
         </is>
       </c>
-      <c r="J83" s="49" t="inlineStr">
+      <c r="J83" s="108" t="inlineStr">
         <is>
           <t>Gij weet in Uw Ziel dat een filosofische transformatie nu meer dan ooit noodzakelijk is.</t>
         </is>
@@ -51122,7 +51145,7 @@
           <t>Sen, İnsanlar'ın değişme yeteneğine sahip olduğunun canlı kanıtısın.</t>
         </is>
       </c>
-      <c r="J85" s="49" t="inlineStr">
+      <c r="J85" s="108" t="inlineStr">
         <is>
           <t>Gij bent het levende bewijs dat Mensen boven zichzelf kunnen stijgen.</t>
         </is>
@@ -51180,7 +51203,7 @@
           <t>İlk durağım Teknopol Büyükşehir olabiliyor mu?</t>
         </is>
       </c>
-      <c r="J86" s="45" t="inlineStr">
+      <c r="J86" s="107" t="inlineStr">
         <is>
           <t>Kan de eerste stop Technopolis zijn?</t>
         </is>
@@ -51934,7 +51957,7 @@
           <t xml:space="preserve">Teknopol Büyükşehir'de görüşürüz. </t>
         </is>
       </c>
-      <c r="J99" s="44" t="inlineStr">
+      <c r="J99" s="106" t="inlineStr">
         <is>
           <t>'k Zie u in Technopolis.</t>
         </is>
@@ -52344,7 +52367,7 @@
           <t xml:space="preserve">O yüzden Teyze ve Dayılar'ın Traktör-Makine'yle onları bulmaya gitti. </t>
         </is>
       </c>
-      <c r="J106" s="49" t="inlineStr">
+      <c r="J106" s="108" t="inlineStr">
         <is>
           <t>Dus je tantes en nonkels zijn met de Tractor-Machine vertrokken om hen te gaan zoeken.</t>
         </is>
@@ -52522,7 +52545,7 @@
           <t>Benimle Teknopol Büyükşehir'e gelir misin?</t>
         </is>
       </c>
-      <c r="J109" s="45" t="inlineStr">
+      <c r="J109" s="107" t="inlineStr">
         <is>
           <t>Wil je met mij mee naar Technopolis?</t>
         </is>
@@ -53752,7 +53775,7 @@
           <t>Kendisi henüz bu Hareket'i desteklemeye hazır değil.</t>
         </is>
       </c>
-      <c r="J130" s="45" t="inlineStr">
+      <c r="J130" s="107" t="inlineStr">
         <is>
           <t>Ze is nog niet klaar om Uw Beweging te steunen.</t>
         </is>
@@ -54042,7 +54065,7 @@
           <t>Git o zaman.</t>
         </is>
       </c>
-      <c r="J135" s="45" t="inlineStr">
+      <c r="J135" s="107" t="inlineStr">
         <is>
           <t>Gaat dan.</t>
         </is>
@@ -54158,7 +54181,7 @@
           <t xml:space="preserve">Ben gelir bulurum seni Teknopol'de. </t>
         </is>
       </c>
-      <c r="J137" s="44" t="inlineStr">
+      <c r="J137" s="106" t="inlineStr">
         <is>
           <t>'k Kom u zoeken in Technopolis.</t>
         </is>
@@ -54920,7 +54943,7 @@
           <t xml:space="preserve">Ben Teknopol Büyükşehir'e gidiyorum. </t>
         </is>
       </c>
-      <c r="J150" s="44" t="inlineStr">
+      <c r="J150" s="106" t="inlineStr">
         <is>
           <t>'k Ga naar Technopolis.</t>
         </is>
